--- a/artfynd/A 46864-2025 artfynd.xlsx
+++ b/artfynd/A 46864-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132785960</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>132785946</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>132785944</v>
       </c>
       <c r="B4" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>132785982</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132785957</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>132785949</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>132785941</v>
       </c>
       <c r="B8" t="n">
-        <v>78334</v>
+        <v>78335</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,6 +1442,1121 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132876114</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91873</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>736797</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7077149</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132876109</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79947</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>736761</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7077276</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132876111</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>736752</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7077214</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132876115</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>736800</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7077129</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132876113</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>736796</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7077153</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132876110</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79947</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>736751</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7077257</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132876106</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>736967</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7077124</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132876112</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>736718</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7077192</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132876107</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91873</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>736923</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7077152</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132876108</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>736923</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7077156</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46864-2025 artfynd.xlsx
+++ b/artfynd/A 46864-2025 artfynd.xlsx
@@ -1448,7 +1448,7 @@
         <v>132876114</v>
       </c>
       <c r="B9" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>132876107</v>
       </c>
       <c r="B17" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 46864-2025 artfynd.xlsx
+++ b/artfynd/A 46864-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>132785946</v>
       </c>
       <c r="B3" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>132785944</v>
       </c>
       <c r="B4" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132785957</v>
       </c>
       <c r="B6" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>132785949</v>
       </c>
       <c r="B7" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>132785941</v>
       </c>
       <c r="B8" t="n">
-        <v>78335</v>
+        <v>78336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>132876114</v>
       </c>
       <c r="B9" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>132876109</v>
       </c>
       <c r="B10" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>132876111</v>
       </c>
       <c r="B11" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>132876115</v>
       </c>
       <c r="B12" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>132876113</v>
       </c>
       <c r="B13" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>132876110</v>
       </c>
       <c r="B14" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>132876112</v>
       </c>
       <c r="B16" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>132876107</v>
       </c>
       <c r="B17" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>132876108</v>
       </c>
       <c r="B18" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 46864-2025 artfynd.xlsx
+++ b/artfynd/A 46864-2025 artfynd.xlsx
@@ -2338,32 +2338,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132876107</v>
+        <v>132876108</v>
       </c>
       <c r="B17" t="n">
-        <v>91876</v>
+        <v>79329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>736923</v>
       </c>
       <c r="R17" t="n">
-        <v>7077152</v>
+        <v>7077156</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,32 +2449,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132876108</v>
+        <v>132876107</v>
       </c>
       <c r="B18" t="n">
-        <v>79329</v>
+        <v>91876</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2491,7 +2491,7 @@
         <v>736923</v>
       </c>
       <c r="R18" t="n">
-        <v>7077156</v>
+        <v>7077152</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 46864-2025 artfynd.xlsx
+++ b/artfynd/A 46864-2025 artfynd.xlsx
@@ -1445,32 +1445,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132876114</v>
+        <v>132876109</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>79953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736797</v>
+        <v>736761</v>
       </c>
       <c r="R9" t="n">
-        <v>7077149</v>
+        <v>7077276</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,32 +1556,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132876109</v>
+        <v>132876114</v>
       </c>
       <c r="B10" t="n">
-        <v>79952</v>
+        <v>91883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736761</v>
+        <v>736797</v>
       </c>
       <c r="R10" t="n">
-        <v>7077276</v>
+        <v>7077149</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,7 +1670,7 @@
         <v>132876111</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>132876115</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>132876113</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>132876110</v>
       </c>
       <c r="B14" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>132876112</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>132876107</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>132876108</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 46864-2025 artfynd.xlsx
+++ b/artfynd/A 46864-2025 artfynd.xlsx
@@ -1445,32 +1445,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132876109</v>
+        <v>132876114</v>
       </c>
       <c r="B9" t="n">
-        <v>79953</v>
+        <v>91883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736761</v>
+        <v>736797</v>
       </c>
       <c r="R9" t="n">
-        <v>7077276</v>
+        <v>7077149</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,32 +1556,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132876114</v>
+        <v>132876109</v>
       </c>
       <c r="B10" t="n">
-        <v>91883</v>
+        <v>79953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736797</v>
+        <v>736761</v>
       </c>
       <c r="R10" t="n">
-        <v>7077149</v>
+        <v>7077276</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 46864-2025 artfynd.xlsx
+++ b/artfynd/A 46864-2025 artfynd.xlsx
@@ -1445,32 +1445,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132876114</v>
+        <v>132876109</v>
       </c>
       <c r="B9" t="n">
-        <v>91883</v>
+        <v>79953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736797</v>
+        <v>736761</v>
       </c>
       <c r="R9" t="n">
-        <v>7077149</v>
+        <v>7077276</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,32 +1556,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132876109</v>
+        <v>132876114</v>
       </c>
       <c r="B10" t="n">
-        <v>79953</v>
+        <v>91883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736761</v>
+        <v>736797</v>
       </c>
       <c r="R10" t="n">
-        <v>7077276</v>
+        <v>7077149</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
